--- a/daily_matches/job_matches_2026-05-11.xlsx
+++ b/daily_matches/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640ad2341149d2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>Software Development (Python)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Copilot, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
+          <t>Generative AI, RAG, Gemini, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0de03440ff246ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist, Upstream Operations</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e8491745c79c989</t>
+          <t>https://www.indeed.com/viewjob?jk=198650efa916c502</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Senior MLOps &amp; Data Systems Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lime</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Tableau, MicroStrategy, Python</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cca72527ec2047e</t>
+          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>API Threat Intelligence Analyst</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Kubernetes, CI/CD, Git, PySpark, Hadoop, PostgreSQL, MySQL, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, Glue, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5bb3f8181d837d9</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f0b56014f96906</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Pinecone, Prompt Engineering, BigQuery, FastAPI, BigQuery, Python, R</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, Glue, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,49 +671,49 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4ed8572a19856a3</t>
+          <t>https://www.indeed.com/viewjob?jk=35fd08830bd17a38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Azure ML, CI/CD, Snowflake, Databricks, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, Hadoop, MySQL, Cassandra, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c3acfa986460bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+          <t>Copilot, Glue, Docker, CI/CD, Jenkins, Git, Snowflake, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ba83bcdfa03dd30</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Backend Software Engineer (Python)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Pinecone, FastAPI, AKS, CI/CD, Python, R, Optimization</t>
+          <t>Prompt Engineering, Kubernetes, CI/CD, Git, PySpark, Hadoop, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9dfac0ff4100021</t>
+          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Pinecone, FastAPI, AKS, CI/CD, Python, R, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Pinecone, Prompt Engineering, BigQuery, FastAPI, BigQuery, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90654b39198e1e31</t>
+          <t>https://www.indeed.com/viewjob?jk=d12b4b8806a0c858</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>FastAPI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Java, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,252 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a23ccfada2a87f</t>
+          <t>https://www.indeed.com/viewjob?jk=423d9a27a81d9caf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior API Engineer (Python)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arcadis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=102de2a4bff314d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer I, Personalization , Minesweeper</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dataflow, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6545cfbb56510c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mobile Developer (iOS and Android)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Circadia Health</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>El Segundo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4efa4ca5474a180</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior ML/LLM Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Pinecone, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95797850b6f3ee05</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb9b564908ed680</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caae71a4490a41e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Backend / Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LVIS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, S3, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1b33145c76b5d91</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Threat Intelligence</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Cortex, TensorFlow, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fa8814de70f45eb</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-11.xlsx
+++ b/daily_matches/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,28 +482,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Hugging Face, ChromaDB, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d0d3f0e671eca1f</t>
+          <t>https://www.indeed.com/viewjob?jk=66f950321ce64a59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Development (Python)</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,28 +517,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, PyTorch, spaCy, NLTK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c572e92f87a5b7a6</t>
+          <t>https://www.indeed.com/viewjob?jk=4f5daf8e9eeae8cb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,38 +552,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, NLTK, Redshift, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198650efa916c502</t>
+          <t>https://www.indeed.com/viewjob?jk=189a198e2257fc24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior MLOps &amp; Data Systems Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>AI Engineer, Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e97637d29d64b4</t>
+          <t>https://www.indeed.com/viewjob?jk=78cb4d11caed672c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Sr. Data Scientist, Field Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, Glue, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Redshift, Redshift, Tableau, Quicksight, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f0b56014f96906</t>
+          <t>https://www.indeed.com/viewjob?jk=85391395020ac3f2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Sr. Data Scientist, Field Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,59 +661,59 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, Glue, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Redshift, Redshift, Tableau, Quicksight, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35fd08830bd17a38</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa18fdfb3718627</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Data Scientist, Field Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, Hadoop, MySQL, Cassandra, NoSQL, SQL</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Redshift, Redshift, Tableau, Quicksight, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b111e44c034f266</t>
+          <t>https://www.indeed.com/viewjob?jk=3cc6c7bea75e82e4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -731,24 +731,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Glue, Docker, CI/CD, Jenkins, Git, Snowflake, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8df2488699249b</t>
+          <t>https://www.indeed.com/viewjob?jk=e855a2a273541f23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Backend Software Engineer (Python)</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,28 +762,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Kubernetes, CI/CD, Git, PySpark, Hadoop, PostgreSQL, MySQL, Python, SQL</t>
+          <t>Data Scientist, LangChain, LLaMA, Prompt Engineering, TensorFlow, PyTorch, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92240e7a4713a4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a8d9c678c2095726</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,63 +797,63 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Pinecone, Prompt Engineering, BigQuery, FastAPI, BigQuery, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, FastAPI, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12b4b8806a0c858</t>
+          <t>https://www.indeed.com/viewjob?jk=f3978042c0d35ef6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FastAPI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Kafka</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423d9a27a81d9caf</t>
+          <t>https://www.indeed.com/viewjob?jk=42dcb2f842c3b2f2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -867,46 +867,46 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python, R</t>
+          <t>Generative AI, RAG, Dataflow, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102de2a4bff314d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2629194c37fa969d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer I, Personalization , Minesweeper</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dataflow, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6545cfbb56510c6</t>
+          <t>https://www.indeed.com/viewjob?jk=0818e5b6f73c7a43</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mobile Developer (iOS and Android)</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Circadia Health</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4efa4ca5474a180</t>
+          <t>https://www.indeed.com/viewjob?jk=e3173e3a22c18623</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior ML/LLM Engineer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Pinecone, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95797850b6f3ee05</t>
+          <t>https://www.indeed.com/viewjob?jk=450395331f34445c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+          <t>Copilot, Synapse, Dataflow, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caae71a4490a41e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c26d7493c6bd8679</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Backend / Full-Stack Software Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LVIS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, S3, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1b33145c76b5d91</t>
+          <t>https://www.indeed.com/viewjob?jk=82f8c89d706e6bc9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Threat Intelligence</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,262 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Cortex, TensorFlow, CI/CD, Python, R, Java, Optimization</t>
+          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa8814de70f45eb</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff9c5f258d04aaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=410c7062135208be</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dc1507fd6adb095</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Environmental Data Science Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Oak Ridge National Laboratory</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Oak Ridge, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Git, PostgreSQL, MySQL, Cassandra, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=797599eb7e32eb7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sr Applied Scientist, Digital Ads , Amazon Digital Advertising</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Git, Hadoop, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=774b846f7a4bf9e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr Applied Scientist, Digital Ads , Amazon Digital Advertising</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Git, Hadoop, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e3b2e85e176b47e</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26a5e1e218e65e70</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1ba35ddf0464dd7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-11.xlsx
+++ b/daily_matches/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Platform &amp; DevOps Engineer</t>
+          <t>AWS Database Engineer / Cloud DBA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Cortex, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Snowflake</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03fc55dd920ed33e</t>
+          <t>https://www.indeed.com/viewjob?jk=17903f6197e334a8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Data Lake, Snowflake, Databricks, BigQuery, Redshift, PostgreSQL, Tableau</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Azure ML, MLflow, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71de8a1a6ca38c9</t>
+          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, XGBoost, LightGBM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0db369fd93fb4f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a899d3773f42581</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Marketing Data Analyst</t>
+          <t>Data Scientist - Machine Learning</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WebstaurantStore</t>
+          <t>Wingstop</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Tableau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4ecacdf2f334b44</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Support &amp; DevOPS Engineer</t>
+          <t>GCP ML Engineer (Vertex AI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kore.ai</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, Kubernetes, AKS, CI/CD, Jenkins, PostgreSQL, MySQL, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, S3, Glue, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43fdee7cf569751d</t>
+          <t>https://www.indeed.com/viewjob?jk=a26d41718ab44d34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Infrastructure Engineer</t>
+          <t>Intern Java Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>SES</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Pinecone, ChromaDB, Prompt Engineering, S3, EC2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,847 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73ead57f96308ca</t>
+          <t>https://www.indeed.com/viewjob?jk=719d8e98511b78bf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Nova AI/ML Data Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RedCloud Consulting</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, BigQuery, CI/CD, Terraform, Git, BigQuery, Tableau</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=718ee5bf46190c60</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nova AI/ML Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RedCloud Consulting</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, BigQuery, CI/CD, Terraform, Git, BigQuery, Tableau</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99201c2b31936144</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CentralReach</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Holmdel, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Wellington Management</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff2c9ed9f0d9a19b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, S3, Glue, Athena, Kubernetes, Git, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AWS API Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, EC2, CI/CD, Jenkins, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3865d36045c48c5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GCP ML Engineer (Vertex AI)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, BigQuery, FastAPI, Docker, CI/CD, Terraform, BigQuery, PySpark, Hadoop</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>S3, Glue, Athena, Data Lake, Kubernetes, CI/CD, Jenkins, Hadoop, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NEXON America</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>El Segundo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Jenkins, Terraform, Git, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Junior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1000bf5afb9c7b5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AWS API Gateway Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bb6bd1c55522d62</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GCP ML Engineer (Vertex AI)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b808111862e26a41</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Technology Specialist</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Xpereince Roofing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Midvale, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Git, Hadoop, Tableau, Power BI, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=597db8ee43a07b66</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Junior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Git, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Junior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Softengine</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Woodland Hills, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Docker, CI/CD, Terraform, Kafka, MongoDB, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd142a6a03f8bba0</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Technology Governance Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83f6649fd4bfd60c</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cloud Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Docker, Kubernetes, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7606e5a3a9e1bfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Junior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Docker, Kubernetes, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3848d05baa74cb56</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Junior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Docker, Kubernetes, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ec501052ef74751</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior GCP ML Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4ee70eb796e788c</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mirantis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Myrtle Point, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, PostgreSQL, MySQL, Cassandra, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab313ca0a77f69f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mirantis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Myrtle Point, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, PostgreSQL, MySQL, Cassandra, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=800a059c733d35ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Machine Learning Scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bayer</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55deae9d17dad48c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-11.xlsx
+++ b/daily_matches/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Database Engineer / Cloud DBA</t>
+          <t>Expert AI &amp; Cloud Development Architect - Office of the CTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>RAG, S3, Kinesis, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17903f6197e334a8</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc8674d85a442c8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Oregon State University</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Corvallis, OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Azure ML, MLflow, Kubernetes, AKS</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Docker, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3349de217fd5b313</t>
+          <t>https://www.indeed.com/viewjob?jk=933518dacc920f09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, XGBoost, LightGBM</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Keras, MLflow, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a899d3773f42581</t>
+          <t>https://www.indeed.com/viewjob?jk=fae30530e8043b01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist - Machine Learning</t>
+          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wingstop</t>
+          <t>FEI Systems</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Tableau</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Data Lake, Kinesis, CI/CD, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4b842829eab81b</t>
+          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, S3, Glue, MLflow, Docker, Kubernetes</t>
+          <t>Data Scientist, Generative AI, RAG, S3, EC2, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26d41718ab44d34</t>
+          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Intern Java Engineer</t>
+          <t>Data &amp; ML Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SES</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Pinecone, ChromaDB, Prompt Engineering, S3, EC2</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=719d8e98511b78bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d5378ca2d10086b6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nova AI/ML Data Engineer</t>
+          <t>Account Solution Engineer - Federal Civilian (All Levels)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RedCloud Consulting</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, BigQuery, CI/CD, Terraform, Git, BigQuery, Tableau</t>
+          <t>RAG, Gemini, S3, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718ee5bf46190c60</t>
+          <t>https://www.indeed.com/viewjob?jk=6a6d1a3c86e08a08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nova AI/ML Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RedCloud Consulting</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, BigQuery, CI/CD, Terraform, Git, BigQuery, Tableau</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Synapse, Docker, Kubernetes, Git, Databricks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99201c2b31936144</t>
+          <t>https://www.indeed.com/viewjob?jk=6772a7a8fc708e7f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2c9ed9f0d9a19b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tyler, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, S3, Glue, Athena, Kubernetes, Git, Hadoop, Python</t>
+          <t>RAG, Copilot, S3, Docker, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a091392ea4f7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=4db5e2aa69ed2eb7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS API Engineer</t>
+          <t>Platform Intelligence Intern</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Zoox</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, EC2, CI/CD, Jenkins, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3865d36045c48c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=1215b837dfd31f44</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
+          <t>SAP iXp Intern - AI Machine Learning</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, FastAPI, Docker, CI/CD, Terraform, BigQuery, PySpark, Hadoop</t>
+          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce22f8b356b35619</t>
+          <t>https://www.indeed.com/viewjob?jk=6acadf4188c1afdd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Patch My PC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S3, Glue, Athena, Data Lake, Kubernetes, CI/CD, Jenkins, Hadoop, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca8e86ee6ca254d</t>
+          <t>https://www.indeed.com/viewjob?jk=0d815027fc2c324b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Software Engineer—Catalog Domain</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NEXON America</t>
+          <t>Protolabs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Maple Plain, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Jenkins, Terraform, Git, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a10d13e5b0f17d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab556d19e4426c4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>DEVELOPER L2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Docker, Git, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,532 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1000bf5afb9c7b5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AWS API Gateway Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bb6bd1c55522d62</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>GCP ML Engineer (Vertex AI)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b808111862e26a41</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AI Technology Specialist</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Xpereince Roofing</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Midvale, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, Copilot, Git, Hadoop, Tableau, Power BI, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=597db8ee43a07b66</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Junior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Docker, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4cd38b1bf92e7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Junior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc382d4bfe919d05</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Backend &amp; Platform Engineer (.NET / AWS)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Softengine</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Woodland Hills, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Docker, CI/CD, Terraform, Kafka, MongoDB, NoSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=055c54c5a52e97d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ada5e44a1685782</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Technology Governance Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Draper, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83f6649fd4bfd60c</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Cloud Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Docker, Kubernetes, Terraform, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7606e5a3a9e1bfe</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Junior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Docker, Kubernetes, Terraform, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3848d05baa74cb56</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Junior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Docker, Kubernetes, Terraform, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec501052ef74751</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior GCP ML Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Terraform, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ee70eb796e788c</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Technical Support Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Mirantis</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Myrtle Point, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, PostgreSQL, MySQL, Cassandra, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab313ca0a77f69f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Technical Support Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Mirantis</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Myrtle Point, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, PostgreSQL, MySQL, Cassandra, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=800a059c733d35ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Machine Learning Scientist</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Bayer</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Git, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55deae9d17dad48c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4db6c227b140a0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-11.xlsx
+++ b/daily_matches/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Expert AI &amp; Cloud Development Architect - Office of the CTO</t>
+          <t>Software Engineer - Finance Tech</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc8674d85a442c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2936ae83866ecfcd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Corvallis, OR, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Docker, Git, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933518dacc920f09</t>
+          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>Inspire11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Keras, MLflow, Docker, CI/CD</t>
+          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fae30530e8043b01</t>
+          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - ML/AI Data Platform (Remote)</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FEI Systems</t>
+          <t>Odyssey Logistics &amp; Technology Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Data Lake, Kinesis, CI/CD, Snowflake, Kafka</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58ce81b6255bf6b</t>
+          <t>https://www.indeed.com/viewjob?jk=6f2d55c2b18bdcbb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Renesas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, S3, EC2, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13da2a0f601ffa5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f0189c8b698cf1c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data &amp; ML Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, Git</t>
+          <t>MLflow, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5378ca2d10086b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Account Solution Engineer - Federal Civilian (All Levels)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Compotech, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Orono, ME, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Gemini, S3, BigQuery, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI</t>
+          <t>RAG, Copilot, TensorFlow, PyTorch, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a6d1a3c86e08a08</t>
+          <t>https://www.indeed.com/viewjob?jk=918964ea40c5f05b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Synapse, Docker, Kubernetes, Git, Databricks</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772a7a8fc708e7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d356634ed65171</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hatch IT</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c41862eb239f163</t>
+          <t>https://www.indeed.com/viewjob?jk=d8306fe662460dbe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tyler, TX, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Git, MySQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db5e2aa69ed2eb7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4c5b16e100204a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform Intelligence Intern</t>
+          <t>Quality Engineer (AI Automation)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1215b837dfd31f44</t>
+          <t>https://www.indeed.com/viewjob?jk=c6965e57f0ca65be</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAP iXp Intern - AI Machine Learning</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>DNS Solutions Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, R, Scala, A/B Testing</t>
+          <t>Data Scientist, Generative AI, RAG, Data Lake, CI/CD, Git, Databricks, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6acadf4188c1afdd</t>
+          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Performance Engineer Sr</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Patch My PC</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d815027fc2c324b</t>
+          <t>https://www.indeed.com/viewjob?jk=ed682df35e1d8dd0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer—Catalog Domain</t>
+          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Protolabs</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Maple Plain, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
+          <t>BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,497 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab556d19e4426c4</t>
+          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DEVELOPER L2</t>
+          <t>Senior Data Scientist &amp; Modeler</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Iberdrola Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Orange, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Data Lake, Snowflake, Databricks, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI/ML Intern - Generative AI &amp; Intelligent Systems</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, GCP Vertex AI, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00da06905f66ddfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Frontend Software Engineer, GKOS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Magnet Forensics</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb14ba4c3ad49df2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Associate, Solutions Designer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Jenkins, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=203fd8d2244ad082</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr Business Data Analyst</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Irving, TX, US USA</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist (8a-5p) Strategic Planning - Johnson City, TN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ballad Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Johnson City, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, Keras, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=848f1909eaf5a0ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Full-Stack / AI Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>KE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, LLaMA, Prompt Engineering, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=641a5211bedcdba4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (APIs for Data Platform) 100% REMOTE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DNS Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Docker, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4db6c227b140a0</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Git, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ec6fb85dd76c411</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Azure Data &amp; AI Architect - Remote US</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>eGroup Enabling Technologies</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Charleston, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, CI/CD, Databricks, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10325d1368f1d7f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Full Stack AI Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CBIZ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, S3, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68fb2b3a10155d04</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Infrastructure engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Writer</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e139fe615d813a86</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Analyst/Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Quest Global</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af2ed842f3b4cfb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IT Data Scientist</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Advocate Aurora Health</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, CI/CD, Git, Python, SQL, R, Bayesian</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f5700898a938214</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cognizant AI Factory Co-Op</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, FAISS, Pinecone, ChromaDB, Prompt Engineering, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=baa7023424104fdb</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-11.xlsx
+++ b/daily_matches/job_matches_2026-05-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer - Finance Tech</t>
+          <t>Full-Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Asurion</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker</t>
+          <t>RAG, Glue, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2936ae83866ecfcd</t>
+          <t>https://www.indeed.com/viewjob?jk=74f3191cc3d47286</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Developer – Intelligent Systems &amp; Integrations</t>
+          <t>Senior Machine Learning Engineer - Fully Remote!</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>KinderCare Learning Companies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Kafka</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Copilot, XGBoost, LightGBM, MLflow, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5727dfe812017a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=38b630719ad31d3a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Inspire11</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Git, Databricks, BigQuery, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcac04dbf474e01b</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1df3e0ee29922c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Odyssey Logistics &amp; Technology Corporation</t>
+          <t>Uniti</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Databricks, Tableau, Power BI, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, XGBoost, Azure ML, Git, Snowflake, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f2d55c2b18bdcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=223e72da1d2a92d1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Renesas</t>
+          <t>Uniti</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, XGBoost, Azure ML, Git, Snowflake, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0189c8b698cf1c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d1b1d5635915de9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr. Data Scientist, Translational Research</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MLflow, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
+          <t>Data Scientist, RAG, Copilot, S3, Docker, Git, Dask, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6fb94b58173aba</t>
+          <t>https://www.indeed.com/viewjob?jk=6f50c89714879035</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Remote / Project-Based Data Engineer for Public-Sector Data Modernization, Dashboards, and AI-Ready</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Compotech, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orono, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, TensorFlow, PyTorch, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python</t>
+          <t>AI Engineer, RAG, BigQuery, Git, Snowflake, BigQuery, PostgreSQL, MySQL, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918964ea40c5f05b</t>
+          <t>https://www.indeed.com/viewjob?jk=f000f4be342c4377</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>AI Engineer, BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3d356634ed65171</t>
+          <t>https://www.indeed.com/viewjob?jk=e56229e27f5c6fd1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Occidental</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, Terraform, NoSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8306fe662460dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=89f9592a818f19f4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>Data Scientist/Statistician</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Intel Corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, Kubernetes, CI/CD, GitHub Actions, Git, Hadoop, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4c5b16e100204a</t>
+          <t>https://www.indeed.com/viewjob?jk=568f3cd2ebaff791</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quality Engineer (AI Automation)</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Pebble Mobility</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6965e57f0ca65be</t>
+          <t>https://www.indeed.com/viewjob?jk=d498ea32d21ff049</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Ready Foods, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Data Lake, CI/CD, Git, Databricks, NoSQL, Python, SQL</t>
+          <t>Data Lake, Git, Databricks, Hadoop, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7663c2a8691261bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3cb05aee21944b5d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Performance Engineer Sr</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Kinetic Automation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, MongoDB, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, RAG, Copilot, Hugging Face, PyTorch, S3, EC2, FastAPI, Docker, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed682df35e1d8dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8657431695bf32c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer - Management and Operations (Remote in US)</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Resultant</t>
+          <t>SmartAdvocate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Databricks, BigQuery, Python</t>
+          <t>LangChain, RAG, EC2, Docker, CI/CD, Jenkins, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126895852cc1414c</t>
+          <t>https://www.indeed.com/viewjob?jk=001c431f02e0a7d6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist &amp; Modeler</t>
+          <t>Sr Applied AI Engineer-Finance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Iberdrola Group</t>
+          <t>Dematic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Orange, CT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Data Lake, Snowflake, Databricks, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Machine Learning Engineer, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Snowflake, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39fab587fb046739</t>
+          <t>https://www.indeed.com/viewjob?jk=cf120ea2de41b8ea</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI/ML Intern - Generative AI &amp; Intelligent Systems</t>
+          <t>Software Engineer 1 (Full-stack)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ensora Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, GCP Vertex AI, PostgreSQL, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00da06905f66ddfc</t>
+          <t>https://www.indeed.com/viewjob?jk=f28036546336a8c7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Frontend Software Engineer, GKOS</t>
+          <t>Senior Autonomy Data Infrastructure and Analytics Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Magnet Forensics</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Cruz, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java</t>
+          <t>RAG, MLflow, Kubernetes, CI/CD, Terraform, Git, Databricks, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb14ba4c3ad49df2</t>
+          <t>https://www.indeed.com/viewjob?jk=6346f3ffeb8c988c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Associate, Solutions Designer</t>
+          <t>Software Engineer, Battery Manufacturing Development</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Jenkins, Git, Python, R, Java</t>
+          <t>Data Scientist, RAG, Redshift, Docker, Kubernetes, Redshift, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203fd8d2244ad082</t>
+          <t>https://www.indeed.com/viewjob?jk=1a3ca33da74683e7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Business Data Analyst</t>
+          <t>Data Analyst, Residential Energy</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, Git, Tableau, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84034a7d15c3899</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c7326ae780738e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist (8a-5p) Strategic Planning - Johnson City, TN</t>
+          <t>Software Engineer — Full-Stack, Workflows &amp; Public Sector Applications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ballad Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Johnson City, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, Keras, Tableau, Power BI, Python, SQL</t>
+          <t>AI Engineer, RAG, S3, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=848f1909eaf5a0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=98a2e7e9949fa1f0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full-Stack / AI Engineer</t>
+          <t>Expert Software Engineer ( AI &amp; Cybersecurity)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>J.B. Hunt</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lowell, AR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, LLaMA, Prompt Engineering, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, Prompt Engineering, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641a5211bedcdba4</t>
+          <t>https://www.indeed.com/viewjob?jk=697def380b03e404</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (APIs for Data Platform) 100% REMOTE</t>
+          <t>Ai full-stack engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DNS Solutions Inc.</t>
+          <t>Robert Moreno</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Git, Kafka, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Pinecone, Docker, Kubernetes, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,217 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec6fb85dd76c411</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Azure Data &amp; AI Architect - Remote US</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>eGroup Enabling Technologies</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Charleston, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Synapse, CI/CD, Databricks, Power BI, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10325d1368f1d7f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Full Stack AI Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CBIZ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, S3, NoSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68fb2b3a10155d04</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Infrastructure engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Writer</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e139fe615d813a86</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Analyst/Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Quest Global</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af2ed842f3b4cfb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>IT Data Scientist</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Advocate Aurora Health</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Oak Brook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Git, Python, SQL, R, Bayesian</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5700898a938214</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Cognizant AI Factory Co-Op</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, FAISS, Pinecone, ChromaDB, Prompt Engineering, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=baa7023424104fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb858ec3f842ac6</t>
         </is>
       </c>
     </row>
